--- a/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
@@ -2764,7 +2764,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -9862,7 +9862,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -10048,7 +10048,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -11206,7 +11206,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -11672,7 +11672,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11796,7 +11796,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11920,7 +11920,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -12262,7 +12262,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -12324,7 +12324,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -12852,7 +12852,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12976,7 +12976,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -13100,7 +13100,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -13442,7 +13442,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -13504,7 +13504,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -13690,7 +13690,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -14094,7 +14094,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -14218,7 +14218,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -14280,7 +14280,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -14684,7 +14684,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -14746,7 +14746,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -14808,7 +14808,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -14870,7 +14870,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -15212,7 +15212,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -15336,7 +15336,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -15398,7 +15398,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -15460,7 +15460,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -15802,7 +15802,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -15864,7 +15864,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -15926,7 +15926,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -15988,7 +15988,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -16050,7 +16050,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -16392,7 +16392,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -16516,7 +16516,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -16578,7 +16578,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -16640,7 +16640,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -16982,7 +16982,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -17044,7 +17044,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -17106,7 +17106,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -17168,7 +17168,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -17230,7 +17230,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -17572,7 +17572,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -17634,7 +17634,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -17696,7 +17696,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -17758,7 +17758,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -17820,7 +17820,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -21547,7 +21547,7 @@
       </c>
       <c r="F314" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G314" s="3" t="inlineStr">
@@ -21902,7 +21902,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -22314,7 +22314,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -23216,7 +23216,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -23558,7 +23558,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -23970,7 +23970,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -24382,7 +24382,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -25276,7 +25276,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -25618,7 +25618,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -25680,7 +25680,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -26022,7 +26022,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -26434,7 +26434,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -26846,7 +26846,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -27258,7 +27258,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -27670,7 +27670,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -27732,7 +27732,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H404" s="5" t="n">
@@ -28074,7 +28074,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H409" s="5" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H410" s="5" t="n">
@@ -28478,7 +28478,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H415" s="5" t="n">
@@ -28890,7 +28890,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H421" s="5" t="n">
@@ -28947,38 +28947,30 @@
       </c>
       <c r="F422" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H422" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I422" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H422" s="5" t="n">
+        <v>14228000</v>
+      </c>
+      <c r="I422" s="5" t="n">
+        <v>25964</v>
       </c>
       <c r="J422" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K422" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L422" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K422" s="5" t="n">
+        <v>14228000</v>
+      </c>
+      <c r="L422" s="5" t="n">
+        <v>25964</v>
       </c>
       <c r="M422" s="3" t="inlineStr">
         <is>
@@ -28987,7 +28979,7 @@
       </c>
       <c r="N422" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -29302,7 +29294,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H427" s="5" t="n">
@@ -29714,7 +29706,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H433" s="5" t="n">
@@ -33026,7 +33018,7 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H481" s="5" t="n">
@@ -33228,7 +33220,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H484" s="5" t="n">
@@ -33710,7 +33702,7 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H491" s="5" t="n">
@@ -34192,7 +34184,7 @@
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H498" s="5" t="n">
@@ -34674,7 +34666,7 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H505" s="5" t="n">
@@ -35156,7 +35148,7 @@
       </c>
       <c r="G512" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H512" s="5" t="n">
@@ -35638,7 +35630,7 @@
       </c>
       <c r="G519" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H519" s="5" t="n">
@@ -36120,7 +36112,7 @@
       </c>
       <c r="G526" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H526" s="5" t="n">
@@ -36602,7 +36594,7 @@
       </c>
       <c r="G533" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H533" s="5" t="n">
@@ -37084,7 +37076,7 @@
       </c>
       <c r="G540" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H540" s="5" t="n">
@@ -38056,7 +38048,7 @@
       </c>
       <c r="G554" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H554" s="5" t="n">
@@ -38538,7 +38530,7 @@
       </c>
       <c r="G561" s="3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="H561" s="5" t="n">
@@ -39020,7 +39012,7 @@
       </c>
       <c r="G568" s="3" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H568" s="5" t="n">
@@ -39502,7 +39494,7 @@
       </c>
       <c r="G575" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H575" s="5" t="n">
@@ -39984,7 +39976,7 @@
       </c>
       <c r="G582" s="3" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="H582" s="5" t="n">
@@ -40466,7 +40458,7 @@
       </c>
       <c r="G589" s="3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="H589" s="5" t="n">
@@ -40948,7 +40940,7 @@
       </c>
       <c r="G596" s="3" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="H596" s="5" t="n">
@@ -41430,7 +41422,7 @@
       </c>
       <c r="G603" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H603" s="5" t="n">
@@ -41912,7 +41904,7 @@
       </c>
       <c r="G610" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H610" s="5" t="n">
@@ -42394,7 +42386,7 @@
       </c>
       <c r="G617" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H617" s="5" t="n">
@@ -42876,7 +42868,7 @@
       </c>
       <c r="G624" s="3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="H624" s="5" t="n">
@@ -43358,7 +43350,7 @@
       </c>
       <c r="G631" s="3" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H631" s="5" t="n">
@@ -44189,7 +44181,7 @@
           <t>A | 819呎 (3房)
 $3054万
 $37,291/呎
-(25年-09月-02日)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -44213,7 +44205,7 @@
           <t>D | 432呎 (2房)
 $1193万
 $27,606/呎
-(26年-06月-23日)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -44268,7 +44260,7 @@
           <t>A | 819呎 (3房)
 $3024万
 $36,921/呎
-(25年-09月-03日)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
@@ -44276,7 +44268,7 @@
           <t>B | 818呎 (3房)
 $3730万
 $45,605/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="D9" s="24" t="inlineStr">
@@ -44284,7 +44276,7 @@
           <t>C | 320呎 (1房)
 $845万
 $26,412/呎
-(26年-07月-22日)</t>
+(26年-07月-23日)</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -44363,7 +44355,7 @@
           <t>C | 320呎 (1房)
 $837万
 $26,150/呎
-(26年-07月-15日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
@@ -44371,7 +44363,7 @@
           <t>D | 432呎 (2房)
 $1169万
 $27,062/呎
-(26年-06月-16日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="F10" s="24" t="inlineStr">
@@ -44379,7 +44371,7 @@
           <t>E | 452呎 (2房)
 $1280万
 $28,330/呎
-(26年-07月-20日)</t>
+(26年-07月-21日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -44426,7 +44418,7 @@
           <t>A | 819呎 (3房)
 $4034万
 $49,252/呎
-(26年-06月-15日)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
@@ -44434,7 +44426,7 @@
           <t>B | 818呎 (3房)
 $3867万
 $47,278/呎
-(26年-06月-15日)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
@@ -44442,7 +44434,7 @@
           <t>C | 320呎 (1房)
 $828万
 $25,891/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
@@ -44450,7 +44442,7 @@
           <t>D | 432呎 (2房)
 $1158万
 $26,796/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -44505,7 +44497,7 @@
           <t>A | 819呎 (3房)
 $3287万
 $40,136/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -44521,7 +44513,7 @@
           <t>C | 320呎 (1房)
 $797万
 $24,903/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
@@ -44529,7 +44521,7 @@
           <t>D | 432呎 (2房)
 $1124万
 $26,019/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -44584,7 +44576,7 @@
           <t>A | 819呎 (3房)
 $3066万
 $37,441/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -44592,7 +44584,7 @@
           <t>B | 818呎 (3房)
 $2950万
 $36,070/呎
-(26年-04月-07日)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="D13" s="24" t="inlineStr">
@@ -44600,7 +44592,7 @@
           <t>C | 320呎 (1房)
 $793万
 $24,778/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">
@@ -44608,7 +44600,7 @@
           <t>D | 432呎 (2房)
 $1096万
 $25,382/呎
-(26年-03月-09日)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="F13" s="24" t="inlineStr">
@@ -44616,7 +44608,7 @@
           <t>E | 452呎 (2房)
 $1226万
 $27,122/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -44663,7 +44655,7 @@
           <t>A | 819呎 (3房)
 $2993万
 $36,545/呎
-(26年-01月-05日)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -44671,7 +44663,7 @@
           <t>B | 818呎 (3房)
 $2991万
 $36,566/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
@@ -44679,7 +44671,7 @@
           <t>C | 320呎 (1房)
 $789万
 $24,656/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -44687,7 +44679,7 @@
           <t>D | 432呎 (2房)
 $1091万
 $25,255/呎
-(26年-03月-09日)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="F14" s="24" t="inlineStr">
@@ -44695,7 +44687,7 @@
           <t>E | 452呎 (2房)
 $1248万
 $27,602/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -44742,7 +44734,7 @@
           <t>A | 819呎 (3房)
 $2949万
 $36,009/呎
-(25年-12月-02日)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -44758,7 +44750,7 @@
           <t>C | 320呎 (1房)
 $770万
 $24,050/呎
-(26年-03月-09日)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
@@ -44766,7 +44758,7 @@
           <t>D | 432呎 (2房)
 $1086万
 $25,130/呎
-(26年-03月-09日)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
@@ -44821,7 +44813,7 @@
           <t>A | 819呎 (3房)
 $2934万
 $35,829/呎
-(25年-10月-26日)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -44829,7 +44821,7 @@
           <t>B | 818呎 (3房)
 $2907万
 $35,533/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
@@ -44837,7 +44829,7 @@
           <t>C | 320呎 (1房)
 $781万
 $24,412/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -44845,7 +44837,7 @@
           <t>D | 432呎 (2房)
 $1102万
 $25,507/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
@@ -44900,7 +44892,7 @@
           <t>A | 819呎 (3房)
 $2920万
 $35,653/呎
-(25年-10月-20日)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
@@ -44908,7 +44900,7 @@
           <t>B | 818呎 (3房)
 $2838万
 $34,689/呎
-(26年-03月-08日)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
@@ -44916,7 +44908,7 @@
           <t>C | 320呎 (1房)
 $777万
 $24,291/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
@@ -44924,7 +44916,7 @@
           <t>D | 432呎 (2房)
 $1096万
 $25,377/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
@@ -44979,7 +44971,7 @@
           <t>A | 819呎 (3房)
 $2906万
 $35,480/呎
-(25年-09月-01日)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -44987,7 +44979,7 @@
           <t>B | 818呎 (3房)
 $2796万
 $34,185/呎
-(26年-02月-23日)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
@@ -44995,7 +44987,7 @@
           <t>C | 320呎 (1房)
 $758万
 $23,694/呎
-(26年-03月-11日)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="E18" s="24" t="inlineStr">
@@ -45003,7 +44995,7 @@
           <t>D | 432呎 (2房)
 $1069万
 $24,755/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
@@ -45058,7 +45050,7 @@
           <t>A | 819呎 (3房)
 $2835万
 $34,613/呎
-(25年-09月-02日)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -45066,7 +45058,7 @@
           <t>B | 818呎 (3房)
 $2702万
 $33,029/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="D19" s="24" t="inlineStr">
@@ -45074,7 +45066,7 @@
           <t>C | 320呎 (1房)
 $770万
 $24,047/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E19" s="24" t="inlineStr">
@@ -45082,7 +45074,7 @@
           <t>D | 432呎 (2房)
 $1064万
 $24,632/呎
-(26年-02月-24日)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="F19" s="24" t="inlineStr">
@@ -45090,7 +45082,7 @@
           <t>E | 452呎 (2房)
 $1167万
 $25,825/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -45137,7 +45129,7 @@
           <t>A | 819呎 (3房)
 $2823万
 $34,466/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -45145,7 +45137,7 @@
           <t>B | 818呎 (3房)
 $2822万
 $34,501/呎
-(26年-03月-09日)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
@@ -45153,7 +45145,7 @@
           <t>C | 319呎 (1房)
 $768万
 $24,066/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
       <c r="E20" s="24" t="inlineStr">
@@ -45161,7 +45153,7 @@
           <t>D | 432呎 (2房)
 $1080万
 $25,000/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="F20" s="24" t="inlineStr">
@@ -45169,7 +45161,7 @@
           <t>E | 452呎 (2房)
 $1162万
 $25,697/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -45295,7 +45287,7 @@
           <t>A | 819呎 (3房)
 $2834万
 $34,601/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -45303,7 +45295,7 @@
           <t>B | 818呎 (3房)
 $2701万
 $33,015/呎
-(26年-01月-01日)</t>
+(26年-01月-02日)</t>
         </is>
       </c>
       <c r="D22" s="24" t="inlineStr">
@@ -45311,7 +45303,7 @@
           <t>C | 320呎 (1房)
 $754万
 $23,569/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="E22" s="24" t="inlineStr">
@@ -45319,7 +45311,7 @@
           <t>D | 432呎 (2房)
 $1064万
 $24,627/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="F22" s="24" t="inlineStr">
@@ -45327,7 +45319,7 @@
           <t>E | 452呎 (2房)
 $1122万
 $24,827/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -45374,7 +45366,7 @@
           <t>A | 819呎 (3房)
 $2792万
 $34,088/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -45382,7 +45374,7 @@
           <t>B | 818呎 (3房)
 $2713万
 $33,171/呎
-(26年-02月-01日)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr">
@@ -45390,7 +45382,7 @@
           <t>C | 320呎 (1房)
 $750万
 $23,453/呎
-(26年-03月-29日)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="E23" s="24" t="inlineStr">
@@ -45398,7 +45390,7 @@
           <t>D | 432呎 (2房)
 $1038万
 $24,021/呎
-(26年-03月-05日)</t>
+(26年-03月-06日)</t>
         </is>
       </c>
       <c r="F23" s="24" t="inlineStr">
@@ -45406,7 +45398,7 @@
           <t>E | 452呎 (2房)
 $1116万
 $24,701/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -45453,7 +45445,7 @@
           <t>A | 819呎 (3房)
 $2751万
 $33,587/呎
-(25年-09月-09日)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -45461,7 +45453,7 @@
           <t>B | 818呎 (3房)
 $2622万
 $32,051/呎
-(25年-08月-28日)</t>
+(25年-08月-29日)</t>
         </is>
       </c>
       <c r="D24" s="24" t="inlineStr">
@@ -45469,7 +45461,7 @@
           <t>C | 320呎 (1房)
 $732万
 $22,875/呎
-(26年-02月-04日)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="E24" s="24" t="inlineStr">
@@ -45477,7 +45469,7 @@
           <t>D | 432呎 (2房)
 $1032万
 $23,900/呎
-(26年-02月-09日)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="F24" s="24" t="inlineStr">
@@ -45485,7 +45477,7 @@
           <t>E | 452呎 (2房)
 $1111万
 $24,577/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -45532,7 +45524,7 @@
           <t>A | 819呎 (3房)
 $2736万
 $33,410/呎
-(25年-09月-09日)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
@@ -45540,7 +45532,7 @@
           <t>B | 818呎 (3房)
 $2608万
 $31,884/呎
-(25年-10月-27日)</t>
+(25年-10月-28日)</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
@@ -45548,7 +45540,7 @@
           <t>C | 320呎 (1房)
 $728万
 $22,762/呎
-(25年-12月-01日)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="E25" s="24" t="inlineStr">
@@ -45556,7 +45548,7 @@
           <t>D | 432呎 (2房)
 $1027万
 $23,782/呎
-(25年-12月-02日)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="F25" s="24" t="inlineStr">
@@ -45564,7 +45556,7 @@
           <t>E | 452呎 (2房)
 $1105万
 $24,456/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -45611,7 +45603,7 @@
           <t>A | 819呎 (3房)
 $2806万
 $34,261/呎
-(25年-11月-02日)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -45619,7 +45611,7 @@
           <t>B | 818呎 (3房)
 $2595万
 $31,724/呎
-(25年-11月-26日)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr">
@@ -45627,7 +45619,7 @@
           <t>C | 320呎 (1房)
 $725万
 $22,647/呎
-(26年-01月-22日)</t>
+(26年-01月-23日)</t>
         </is>
       </c>
       <c r="E26" s="24" t="inlineStr">
@@ -45635,7 +45627,7 @@
           <t>D | 432呎 (2房)
 $1022万
 $23,664/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="F26" s="24" t="inlineStr">
@@ -45643,7 +45635,7 @@
           <t>E | 452呎 (2房)
 $1100万
 $24,332/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -45690,7 +45682,7 @@
           <t>A | 819呎 (3房)
 $2792万
 $34,090/呎
-(25年-11月-16日)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
@@ -45698,7 +45690,7 @@
           <t>B | 818呎 (3房)
 $2582万
 $31,565/呎
-(25年-12月-30日)</t>
+(25年-12月-31日)</t>
         </is>
       </c>
       <c r="D27" s="24" t="inlineStr">
@@ -45706,7 +45698,7 @@
           <t>C | 320呎 (1房)
 $721万
 $22,534/呎
-(26年-01月-13日)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="E27" s="24" t="inlineStr">
@@ -45714,7 +45706,7 @@
           <t>D | 432呎 (2房)
 $1017万
 $23,544/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
       <c r="F27" s="24" t="inlineStr">
@@ -45722,7 +45714,7 @@
           <t>E | 452呎 (2房)
 $1094万
 $24,210/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -45769,7 +45761,7 @@
           <t>A | 819呎 (3房)
 $2722万
 $33,242/呎
-(25年-10月-21日)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
@@ -45777,7 +45769,7 @@
           <t>B | 818呎 (3房)
 $2569万
 $31,407/呎
-(26年-01月-07日)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="D28" s="24" t="inlineStr">
@@ -45785,7 +45777,7 @@
           <t>C | 320呎 (1房)
 $718万
 $22,422/呎
-(26年-01月-14日)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="E28" s="24" t="inlineStr">
@@ -45793,7 +45785,7 @@
           <t>D | 432呎 (2房)
 $1022万
 $23,662/呎
-(26年-03月-05日)</t>
+(26年-03月-06日)</t>
         </is>
       </c>
       <c r="F28" s="24" t="inlineStr">
@@ -45801,7 +45793,7 @@
           <t>E | 452呎 (2房)
 $1089万
 $24,091/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -45848,7 +45840,7 @@
           <t>A | 819呎 (3房)
 $2682万
 $32,744/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
@@ -45856,7 +45848,7 @@
           <t>B | 818呎 (3房)
 $2531万
 $30,936/呎
-(26年-01月-04日)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
       <c r="D29" s="24" t="inlineStr">
@@ -45864,7 +45856,7 @@
           <t>C | 320呎 (1房)
 $707万
 $22,084/呎
-(25年-12月-22日)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="E29" s="24" t="inlineStr">
@@ -45872,7 +45864,7 @@
           <t>D | 432呎 (2房)
 $1007万
 $23,308/呎
-(26年-03月-05日)</t>
+(26年-03月-06日)</t>
         </is>
       </c>
       <c r="F29" s="24" t="inlineStr">
@@ -45880,7 +45872,7 @@
           <t>E | 452呎 (2房)
 $1073万
 $23,730/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -45927,7 +45919,7 @@
           <t>A | 819呎 (3房)
 $2629万
 $32,098/呎
-(25年-09月-01日)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
@@ -45935,7 +45927,7 @@
           <t>B | 818呎 (3房)
 $2505万
 $30,627/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="D30" s="24" t="inlineStr">
@@ -45943,7 +45935,7 @@
           <t>C | 319呎 (1房)
 $716万
 $22,433/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="E30" s="24" t="inlineStr">
@@ -45951,7 +45943,7 @@
           <t>D | 432呎 (2房)
 $987万
 $22,845/呎
-(25年-12月-22日)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="F30" s="24" t="inlineStr">
@@ -45959,7 +45951,7 @@
           <t>E | 452呎 (2房)
 $1062万
 $23,493/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -46006,7 +45998,7 @@
           <t>A | 819呎 (3房)
 $2603万
 $31,780/呎
-(25年-09月-09日)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
@@ -46014,7 +46006,7 @@
           <t>B | 818呎 (3房)
 $2480万
 $30,320/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="D31" s="24" t="inlineStr">
@@ -46022,7 +46014,7 @@
           <t>C | 319呎 (1房)
 $708万
 $22,207/呎
-(26年-01月-06日)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="E31" s="24" t="inlineStr">
@@ -46030,7 +46022,7 @@
           <t>D | 431呎 (2房)
 $999万
 $23,183/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
       <c r="F31" s="24" t="inlineStr">
@@ -46038,7 +46030,7 @@
           <t>E | 452呎 (2房)
 $1051万
 $23,257/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -46085,7 +46077,7 @@
           <t>A | 819呎 (3房)
 $2563万
 $31,297/呎
-(25年-09月-14日)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
@@ -46093,7 +46085,7 @@
           <t>B | 818呎 (3房)
 $2443万
 $29,866/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="D32" s="24" t="inlineStr">
@@ -46101,7 +46093,7 @@
           <t>C | 320呎 (1房)
 $682万
 $21,322/呎
-(25年-12月-02日)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="E32" s="24" t="inlineStr">
@@ -46109,7 +46101,7 @@
           <t>D | 432呎 (2房)
 $962万
 $22,278/呎
-(26年-01月-07日)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="F32" s="24" t="inlineStr">
@@ -46117,7 +46109,7 @@
           <t>E | 452呎 (2房)
 $1036万
 $22,909/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -46164,7 +46156,7 @@
           <t>A | 819呎 (3房)
 $2525万
 $30,827/呎
-(25年-10月-21日)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
@@ -46172,7 +46164,7 @@
           <t>B | 818呎 (3房)
 $2406万
 $29,418/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="D33" s="24" t="inlineStr">
@@ -46180,7 +46172,7 @@
           <t>C | 320呎 (1房)
 $672万
 $21,000/呎
-(26年-01月-13日)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="E33" s="24" t="inlineStr">
@@ -46188,7 +46180,7 @@
           <t>D | 432呎 (2房)
 $948万
 $21,942/呎
-(26年-01月-11日)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="F33" s="24" t="inlineStr">
@@ -46196,7 +46188,7 @@
           <t>E | 452呎 (2房)
 $1020万
 $22,564/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -46306,17 +46298,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -46813,12 +46805,12 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>A | 548呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -46881,7 +46873,7 @@
           <t>B | 449呎 (2房)
 $1251万
 $27,853/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -46936,7 +46928,7 @@
           <t>B | 449呎 (2房)
 $1198万
 $26,670/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -47038,7 +47030,7 @@
           <t>A | 548呎 (2房)
 $1565万
 $28,560/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -47101,7 +47093,7 @@
           <t>B | 449呎 (2房)
 $1180万
 $26,274/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -47156,7 +47148,7 @@
           <t>B | 449呎 (2房)
 $1151万
 $25,628/呎
-(25年-11月-26日)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -47211,7 +47203,7 @@
           <t>B | 449呎 (2房)
 $1145万
 $25,501/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -47313,7 +47305,7 @@
           <t>A | 548呎 (2房)
 $1519万
 $27,714/呎
-(26年-07月-12日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -47321,7 +47313,7 @@
           <t>B | 449呎 (2房)
 $1150万
 $25,624/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -47368,7 +47360,7 @@
           <t>A | 548呎 (2房)
 $1511万
 $27,577/呎
-(26年-06月-20日)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -47376,7 +47368,7 @@
           <t>B | 449呎 (2房)
 $1145万
 $25,494/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -47431,7 +47423,7 @@
           <t>B | 449呎 (2房)
 $1139万
 $25,367/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -47486,7 +47478,7 @@
           <t>B | 449呎 (2房)
 $1111万
 $24,744/呎
-(26年-02月-03日)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -47541,7 +47533,7 @@
           <t>B | 449呎 (2房)
 $1106万
 $24,621/呎
-(25年-12月-29日)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -47596,7 +47588,7 @@
           <t>B | 449呎 (2房)
 $1100万
 $24,499/呎
-(25年-12月-30日)</t>
+(25年-12月-31日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -47643,7 +47635,7 @@
           <t>A | 548呎 (2房)
 $1474万
 $26,894/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
@@ -47651,7 +47643,7 @@
           <t>B | 449呎 (2房)
 $1116万
 $24,864/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -47698,7 +47690,7 @@
           <t>A | 548呎 (2房)
 $1452万
 $26,489/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
@@ -47706,7 +47698,7 @@
           <t>B | 449呎 (2房)
 $1078万
 $24,009/呎
-(26年-02月-03日)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -47761,7 +47753,7 @@
           <t>B | 449呎 (2房)
 $1089万
 $24,247/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -47803,12 +47795,12 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>A | 548呎 (2房)
-招标单位
--
-(已定价未售)</t>
+$1423万
+$25,964/呎
+(26年-07月-27日)</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
@@ -47816,7 +47808,7 @@
           <t>B | 449呎 (2房)
 $1057万
 $23,532/呎
-(25年-12月-02日)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -47871,7 +47863,7 @@
           <t>B | 449呎 (2房)
 $1041万
 $23,178/呎
-(25年-12月-23日)</t>
+(25年-12月-24日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -47926,7 +47918,7 @@
           <t>B | 449呎 (2房)
 $1025万
 $22,831/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -48508,7 +48500,7 @@
           <t>C | 309呎 (1房)
 $828万
 $26,812/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -48603,7 +48595,7 @@
           <t>G | 513呎 (2房)
 $1591万
 $31,006/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
     </row>
@@ -48666,7 +48658,7 @@
           <t>G | 513呎 (2房)
 $1553万
 $30,281/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -48729,7 +48721,7 @@
           <t>G | 513呎 (2房)
 $1487万
 $28,992/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -48792,7 +48784,7 @@
           <t>G | 513呎 (2房)
 $1538万
 $29,979/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
     </row>
@@ -48855,7 +48847,7 @@
           <t>G | 513呎 (2房)
 $1501万
 $29,267/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
     </row>
@@ -48918,7 +48910,7 @@
           <t>G | 513呎 (2房)
 $1494万
 $29,121/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -48981,7 +48973,7 @@
           <t>G | 513呎 (2房)
 $1458万
 $28,419/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
     </row>
@@ -49044,7 +49036,7 @@
           <t>G | 513呎 (2房)
 $1451万
 $28,279/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
     </row>
@@ -49107,7 +49099,7 @@
           <t>G | 513呎 (2房)
 $1443万
 $28,135/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -49233,7 +49225,7 @@
           <t>G | 513呎 (2房)
 $1422万
 $27,715/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -49296,7 +49288,7 @@
           <t>G | 513呎 (2房)
 $1387万
 $27,035/呎
-(26年-01月-05日)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
     </row>
@@ -49359,7 +49351,7 @@
           <t>G | 513呎 (2房)
 $1380万
 $26,901/呎
-(26年-01月-11日)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
     </row>
@@ -49422,7 +49414,7 @@
           <t>G | 513呎 (2房)
 $1373万
 $26,766/呎
-(26年-01月-19日)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
     </row>
@@ -49485,7 +49477,7 @@
           <t>G | 513呎 (2房)
 $1366万
 $26,632/呎
-(25年-12月-29日)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
     </row>
@@ -49548,7 +49540,7 @@
           <t>G | 513呎 (2房)
 $1359万
 $26,499/呎
-(25年-12月-28日)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
     </row>
@@ -49611,7 +49603,7 @@
           <t>G | 513呎 (2房)
 $1353万
 $26,366/呎
-(26年-01月-04日)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
     </row>
@@ -49674,7 +49666,7 @@
           <t>G | 513呎 (2房)
 $1347万
 $26,265/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -49737,7 +49729,7 @@
           <t>G | 513呎 (2房)
 $1334万
 $26,004/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -49800,7 +49792,7 @@
           <t>G | 513呎 (2房)
 $1306万
 $25,454/呎
-(25年-12月-23日)</t>
+(25年-12月-24日)</t>
         </is>
       </c>
     </row>
@@ -49863,7 +49855,7 @@
           <t>G | 513呎 (2房)
 $1286万
 $25,072/呎
-(25年-12月-28日)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
     </row>
@@ -49926,7 +49918,7 @@
           <t>G | 513呎 (2房)
 $1267万
 $24,696/呎
-(26年-01月-11日)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
     </row>

--- a/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
@@ -33220,7 +33220,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="H484" s="5" t="n">
@@ -48595,7 +48595,7 @@
           <t>G | 513呎 (2房)
 $1591万
 $31,006/呎
-(26年-07月-10日)</t>
+(26年-07月-31日)</t>
         </is>
       </c>
     </row>

--- a/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
@@ -26903,38 +26903,30 @@
       </c>
       <c r="F392" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H392" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I392" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H392" s="5" t="n">
+        <v>14886000</v>
+      </c>
+      <c r="I392" s="5" t="n">
+        <v>27164</v>
       </c>
       <c r="J392" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K392" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L392" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K392" s="5" t="n">
+        <v>14886000</v>
+      </c>
+      <c r="L392" s="5" t="n">
+        <v>27164</v>
       </c>
       <c r="M392" s="3" t="inlineStr">
         <is>
@@ -26943,7 +26935,7 @@
       </c>
       <c r="N392" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -46298,7 +46290,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -46308,7 +46300,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -47520,12 +47512,12 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="24" t="inlineStr">
         <is>
           <t>A | 548呎 (2房)
-招标单位
--
-(在售)</t>
+$1489万
+$27,164/呎
+(26年-07月-30日)</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">

--- a/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
@@ -26079,7 +26079,7 @@
       </c>
       <c r="F380" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G380" s="3" t="inlineStr">
@@ -26089,12 +26089,12 @@
       </c>
       <c r="H380" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I380" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J380" s="3" t="inlineStr">
@@ -26104,12 +26104,12 @@
       </c>
       <c r="K380" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L380" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M380" s="3" t="inlineStr">
@@ -26119,7 +26119,7 @@
       </c>
       <c r="N380" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -26491,7 +26491,7 @@
       </c>
       <c r="F386" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G386" s="3" t="inlineStr">
@@ -26501,12 +26501,12 @@
       </c>
       <c r="H386" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I386" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J386" s="3" t="inlineStr">
@@ -26516,12 +26516,12 @@
       </c>
       <c r="K386" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L386" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M386" s="3" t="inlineStr">
@@ -26531,7 +26531,7 @@
       </c>
       <c r="N386" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -28527,7 +28527,7 @@
       </c>
       <c r="F416" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G416" s="3" t="inlineStr">
@@ -28537,12 +28537,12 @@
       </c>
       <c r="H416" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I416" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J416" s="3" t="inlineStr">
@@ -28552,12 +28552,12 @@
       </c>
       <c r="K416" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L416" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M416" s="3" t="inlineStr">
@@ -28567,7 +28567,7 @@
       </c>
       <c r="N416" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -29343,38 +29343,30 @@
       </c>
       <c r="F428" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H428" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I428" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H428" s="5" t="n">
+        <v>14014000</v>
+      </c>
+      <c r="I428" s="5" t="n">
+        <v>25573</v>
       </c>
       <c r="J428" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K428" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L428" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K428" s="5" t="n">
+        <v>14014000</v>
+      </c>
+      <c r="L428" s="5" t="n">
+        <v>25573</v>
       </c>
       <c r="M428" s="3" t="inlineStr">
         <is>
@@ -29383,7 +29375,7 @@
       </c>
       <c r="N428" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -46290,7 +46282,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -46300,7 +46292,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -46310,7 +46302,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>130</t>
         </is>
       </c>
     </row>
@@ -47402,12 +47394,12 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>A | 548呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -47457,12 +47449,12 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>A | 548呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
@@ -47732,12 +47724,12 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>A | 548呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
@@ -47842,12 +47834,12 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B32" s="23" t="inlineStr">
+      <c r="B32" s="24" t="inlineStr">
         <is>
           <t>A | 548呎 (2房)
-招标单位
--
-(在售)</t>
+$1401万
+$25,573/呎
+(26年-08月-02日)</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">

--- a/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
@@ -15917,7 +15917,7 @@
         </is>
       </c>
       <c r="E231" s="4" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         <v>7156000</v>
       </c>
       <c r="I231" s="5" t="n">
-        <v>22433</v>
+        <v>22362</v>
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>7156000</v>
       </c>
       <c r="L231" s="5" t="n">
-        <v>22433</v>
+        <v>22362</v>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
@@ -45916,9 +45916,9 @@
       </c>
       <c r="D30" s="24" t="inlineStr">
         <is>
-          <t>C | 319呎 (1房)
+          <t>C | 320呎 (1房)
 $716万
-$22,433/呎
+$22,362/呎
 (26年-01月-09日)</t>
         </is>
       </c>

--- a/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
@@ -28944,7 +28944,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H422" s="5" t="n">
@@ -47784,7 +47784,7 @@
           <t>A | 548呎 (2房)
 $1423万
 $25,964/呎
-(26年-07月-27日)</t>
+(26年-08月-24日)</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">

--- a/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
@@ -26491,38 +26491,30 @@
       </c>
       <c r="F386" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H386" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I386" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H386" s="5" t="n">
+        <v>14960000</v>
+      </c>
+      <c r="I386" s="5" t="n">
+        <v>27299</v>
       </c>
       <c r="J386" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K386" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L386" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K386" s="5" t="n">
+        <v>14960000</v>
+      </c>
+      <c r="L386" s="5" t="n">
+        <v>27299</v>
       </c>
       <c r="M386" s="3" t="inlineStr">
         <is>
@@ -26531,7 +26523,7 @@
       </c>
       <c r="N386" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -26908,7 +26900,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -46282,7 +46274,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -46292,7 +46284,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -47449,12 +47441,12 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="24" t="inlineStr">
         <is>
           <t>A | 548呎 (2房)
-招标单位
--
-(在售)</t>
+$1496万
+$27,299/呎
+(26年-08月-23日)</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
@@ -47509,7 +47501,7 @@
           <t>A | 548呎 (2房)
 $1489万
 $27,164/呎
-(26年-07月-30日)</t>
+(26年-08月-24日)</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">

--- a/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
@@ -27299,38 +27299,30 @@
       </c>
       <c r="F398" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H398" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I398" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="H398" s="5" t="n">
+        <v>14812000</v>
+      </c>
+      <c r="I398" s="5" t="n">
+        <v>27029</v>
       </c>
       <c r="J398" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K398" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L398" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K398" s="5" t="n">
+        <v>14812000</v>
+      </c>
+      <c r="L398" s="5" t="n">
+        <v>27029</v>
       </c>
       <c r="M398" s="3" t="inlineStr">
         <is>
@@ -27339,7 +27331,7 @@
       </c>
       <c r="N398" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -46274,7 +46266,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -46284,7 +46276,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -47551,12 +47543,12 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>A | 548呎 (2房)
-招标单位
--
-(在售)</t>
+$1481万
+$27,029/呎
+(26年-08月-25日)</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">

--- a/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
@@ -31667,7 +31667,7 @@
       </c>
       <c r="F462" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G462" s="3" t="inlineStr">
@@ -31677,12 +31677,12 @@
       </c>
       <c r="H462" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I462" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J462" s="3" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="K462" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L462" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M462" s="3" t="inlineStr">
@@ -31707,7 +31707,7 @@
       </c>
       <c r="N462" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -32157,7 +32157,7 @@
       </c>
       <c r="F469" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G469" s="3" t="inlineStr">
@@ -32167,12 +32167,12 @@
       </c>
       <c r="H469" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I469" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J469" s="3" t="inlineStr">
@@ -32182,12 +32182,12 @@
       </c>
       <c r="K469" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L469" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M469" s="3" t="inlineStr">
@@ -32197,7 +32197,7 @@
       </c>
       <c r="N469" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -35453,7 +35453,7 @@
       </c>
       <c r="F517" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G517" s="3" t="inlineStr">
@@ -35463,12 +35463,12 @@
       </c>
       <c r="H517" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I517" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J517" s="3" t="inlineStr">
@@ -35478,12 +35478,12 @@
       </c>
       <c r="K517" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L517" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M517" s="3" t="inlineStr">
@@ -35493,7 +35493,7 @@
       </c>
       <c r="N517" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -35523,7 +35523,7 @@
       </c>
       <c r="F518" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G518" s="3" t="inlineStr">
@@ -35533,12 +35533,12 @@
       </c>
       <c r="H518" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I518" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J518" s="3" t="inlineStr">
@@ -35548,12 +35548,12 @@
       </c>
       <c r="K518" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L518" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M518" s="3" t="inlineStr">
@@ -35563,7 +35563,7 @@
       </c>
       <c r="N518" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -35935,7 +35935,7 @@
       </c>
       <c r="F524" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G524" s="3" t="inlineStr">
@@ -35945,12 +35945,12 @@
       </c>
       <c r="H524" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I524" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J524" s="3" t="inlineStr">
@@ -35960,12 +35960,12 @@
       </c>
       <c r="K524" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L524" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M524" s="3" t="inlineStr">
@@ -35975,7 +35975,7 @@
       </c>
       <c r="N524" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -36005,7 +36005,7 @@
       </c>
       <c r="F525" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G525" s="3" t="inlineStr">
@@ -36015,12 +36015,12 @@
       </c>
       <c r="H525" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I525" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J525" s="3" t="inlineStr">
@@ -36030,12 +36030,12 @@
       </c>
       <c r="K525" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L525" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M525" s="3" t="inlineStr">
@@ -36045,7 +36045,7 @@
       </c>
       <c r="N525" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -38835,7 +38835,7 @@
       </c>
       <c r="F566" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G566" s="3" t="inlineStr">
@@ -38845,12 +38845,12 @@
       </c>
       <c r="H566" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I566" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J566" s="3" t="inlineStr">
@@ -38860,12 +38860,12 @@
       </c>
       <c r="K566" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L566" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M566" s="3" t="inlineStr">
@@ -38875,7 +38875,7 @@
       </c>
       <c r="N566" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -38905,7 +38905,7 @@
       </c>
       <c r="F567" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G567" s="3" t="inlineStr">
@@ -38915,12 +38915,12 @@
       </c>
       <c r="H567" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I567" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J567" s="3" t="inlineStr">
@@ -38930,12 +38930,12 @@
       </c>
       <c r="K567" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L567" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M567" s="3" t="inlineStr">
@@ -38945,7 +38945,7 @@
       </c>
       <c r="N567" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -39317,7 +39317,7 @@
       </c>
       <c r="F573" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G573" s="3" t="inlineStr">
@@ -39327,12 +39327,12 @@
       </c>
       <c r="H573" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I573" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J573" s="3" t="inlineStr">
@@ -39342,12 +39342,12 @@
       </c>
       <c r="K573" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L573" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M573" s="3" t="inlineStr">
@@ -39357,7 +39357,7 @@
       </c>
       <c r="N573" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -39387,7 +39387,7 @@
       </c>
       <c r="F574" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G574" s="3" t="inlineStr">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="H574" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I574" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J574" s="3" t="inlineStr">
@@ -39412,12 +39412,12 @@
       </c>
       <c r="K574" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L574" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M574" s="3" t="inlineStr">
@@ -39427,7 +39427,7 @@
       </c>
       <c r="N574" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -42209,7 +42209,7 @@
       </c>
       <c r="F615" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G615" s="3" t="inlineStr">
@@ -42219,12 +42219,12 @@
       </c>
       <c r="H615" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I615" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J615" s="3" t="inlineStr">
@@ -42234,12 +42234,12 @@
       </c>
       <c r="K615" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L615" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M615" s="3" t="inlineStr">
@@ -42249,7 +42249,7 @@
       </c>
       <c r="N615" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -42279,7 +42279,7 @@
       </c>
       <c r="F616" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G616" s="3" t="inlineStr">
@@ -42289,12 +42289,12 @@
       </c>
       <c r="H616" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I616" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J616" s="3" t="inlineStr">
@@ -42304,12 +42304,12 @@
       </c>
       <c r="K616" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L616" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M616" s="3" t="inlineStr">
@@ -42319,7 +42319,7 @@
       </c>
       <c r="N616" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -42691,7 +42691,7 @@
       </c>
       <c r="F622" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G622" s="3" t="inlineStr">
@@ -42701,12 +42701,12 @@
       </c>
       <c r="H622" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I622" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J622" s="3" t="inlineStr">
@@ -42716,12 +42716,12 @@
       </c>
       <c r="K622" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L622" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M622" s="3" t="inlineStr">
@@ -42731,7 +42731,7 @@
       </c>
       <c r="N622" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -42761,7 +42761,7 @@
       </c>
       <c r="F623" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G623" s="3" t="inlineStr">
@@ -42771,12 +42771,12 @@
       </c>
       <c r="H623" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I623" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J623" s="3" t="inlineStr">
@@ -42786,12 +42786,12 @@
       </c>
       <c r="K623" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L623" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M623" s="3" t="inlineStr">
@@ -42801,7 +42801,7 @@
       </c>
       <c r="N623" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -47997,7 +47997,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -48017,7 +48017,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>160</t>
         </is>
       </c>
     </row>
@@ -48258,12 +48258,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -48321,12 +48321,12 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -48762,20 +48762,20 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -48825,20 +48825,20 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -49203,20 +49203,20 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -49266,20 +49266,20 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -49644,20 +49644,20 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -49707,20 +49707,20 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B31" s="20" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
